--- a/StructureDefinition-Laboratorieanalysresultat-Observation.xlsx
+++ b/StructureDefinition-Laboratorieanalysresultat-Observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
     <t>Laboratorieanalysresultat-Observation.varde</t>
   </si>
   <si>
-    <t xml:space="preserve">base64Binary
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>

--- a/StructureDefinition-Laboratorieanalysresultat-Observation.xlsx
+++ b/StructureDefinition-Laboratorieanalysresultat-Observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Laboratorieanalysresultat : Observation).</t>
+    <t>Klassen Laboratorieanalysresultat håller information om resultat av en utförd analys.
+Detta resultat kan exempelvis bestå av ett mätvärde inom laboratoriedisciplinen kemi, ett fynd av en viss bakterieart eller en textuell beskrivning av analysresultatet. Utöver detta kan en kommentar avseende analysresultatet anges separat.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -260,6 +261,9 @@
     <t>Source attribute: typ</t>
   </si>
   <si>
+    <t>Kod för typ av laboratorieanalysresultat.</t>
+  </si>
+  <si>
     <t>Laboratorieanalysresultat-Observation.varde</t>
   </si>
   <si>
@@ -270,6 +274,10 @@
     <t>Source attribute: värde</t>
   </si>
   <si>
+    <t>Angivelse av utfall av en utförd analys.
+PQ|IVL&lt;PQ&gt;|ST|CV</t>
+  </si>
+  <si>
     <t>Laboratorieanalysresultat-Observation.kommentar</t>
   </si>
   <si>
@@ -280,10 +288,17 @@
     <t>Source attribute: kommentar</t>
   </si>
   <si>
+    <t>Angivelse av kommentar som rör laboratorieanalysresultatet.</t>
+  </si>
+  <si>
     <t>Laboratorieanalysresultat-Observation.tolkning</t>
   </si>
   <si>
     <t>Source attribute: tolkning</t>
+  </si>
+  <si>
+    <t>Kod för en tolkning av laboratorieanalysresultatet.  
+En sådan tolkning kan vara att analysresultatet ligger utanför aktuellt referensintervall, vilket även benämns som patologisk markör.</t>
   </si>
   <si>
     <t>Laboratorieanalysresultat-Observation.negation</t>
@@ -921,7 +936,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -989,10 +1004,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1015,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1072,7 +1087,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1089,10 +1104,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1115,13 +1130,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1172,7 +1187,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1189,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1218,10 +1233,10 @@
         <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1272,7 +1287,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1289,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1315,13 +1330,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1372,7 +1387,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1389,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1415,13 +1430,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1472,7 +1487,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1489,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1515,13 +1530,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1572,7 +1587,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1589,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1615,13 +1630,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1672,7 +1687,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1689,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1715,13 +1730,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1772,7 +1787,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1789,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1815,13 +1830,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1872,7 +1887,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
